--- a/Excel/AchievementTaskGroupConfig.xlsx
+++ b/Excel/AchievementTaskGroupConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
   <si>
     <t>_id</t>
   </si>
@@ -47,10 +47,10 @@
     <t>新入世界</t>
   </si>
   <si>
-    <t>#</t>
+    <t>小试牛刀</t>
   </si>
   <si>
-    <t>小试牛刀</t>
+    <t>#</t>
   </si>
   <si>
     <t>初露锋芒</t>
@@ -1059,25 +1059,19 @@
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="1:4">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" s="3" customFormat="1" customHeight="1" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="1">
         <v>3</v>

--- a/Excel/AchievementTaskGroupConfig.xlsx
+++ b/Excel/AchievementTaskGroupConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>_id</t>
   </si>
@@ -48,9 +53,6 @@
   </si>
   <si>
     <t>小试牛刀</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
   <si>
     <t>初露锋芒</t>
@@ -1018,7 +1020,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:D10"/>
+  <dimension ref="C3:D10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1026,7 +1028,7 @@
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:4">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:4">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1034,7 +1036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:4">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:4">
       <c r="C4" s="4" t="s">
         <v>2</v>
       </c>
@@ -1042,7 +1044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:4">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:4">
       <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
@@ -1050,7 +1052,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:4">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:4">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1058,7 +1060,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:4">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:4">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1066,24 +1068,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" s="3" customFormat="1" customHeight="1" spans="1:4">
-      <c r="A8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>7</v>
-      </c>
+    <row r="8" s="3" customFormat="1" customHeight="1" spans="3:4">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="9" s="3" customFormat="1" customHeight="1" spans="1:4">
+    <row r="9" s="3" customFormat="1" customHeight="1" spans="3:4">
       <c r="C9" s="1"/>
     </row>
-    <row r="10" s="3" customFormat="1" customHeight="1" spans="1:4">
+    <row r="10" s="3" customFormat="1" customHeight="1" spans="3:4">
       <c r="C10" s="1"/>
     </row>
   </sheetData>

--- a/Excel/AchievementTaskGroupConfig.xlsx
+++ b/Excel/AchievementTaskGroupConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>_id</t>
   </si>
@@ -56,6 +56,12 @@
   </si>
   <si>
     <t>初露锋芒</t>
+  </si>
+  <si>
+    <t>每日任务</t>
+  </si>
+  <si>
+    <t>福利任务</t>
   </si>
 </sst>
 </file>
@@ -1020,7 +1026,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:D10"/>
+  <dimension ref="C3:D20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1078,9 +1084,59 @@
     </row>
     <row r="9" s="3" customFormat="1" customHeight="1" spans="3:4">
       <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
     </row>
     <row r="10" s="3" customFormat="1" customHeight="1" spans="3:4">
       <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" s="3" customFormat="1" customHeight="1" spans="3:4">
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" s="3" customFormat="1" customHeight="1" spans="3:4">
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" s="3" customFormat="1" customHeight="1" spans="3:4">
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" s="3" customFormat="1" customHeight="1" spans="3:4">
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" s="3" customFormat="1" customHeight="1" spans="3:4">
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" s="3" customFormat="1" customHeight="1" spans="3:4">
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" s="3" customFormat="1" customHeight="1" spans="3:4">
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" s="3" customFormat="1" customHeight="1" spans="3:4">
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" s="3" customFormat="1" customHeight="1" spans="3:4">
+      <c r="C19" s="1">
+        <v>11</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" s="3" customFormat="1" customHeight="1" spans="3:4">
+      <c r="C20" s="1">
+        <v>12</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/AchievementTaskGroupConfig.xlsx
+++ b/Excel/AchievementTaskGroupConfig.xlsx
@@ -32,12 +32,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t>_id</t>
   </si>
   <si>
     <t>Name</t>
+  </si>
+  <si>
+    <t>RequireLevel</t>
   </si>
   <si>
     <t>Id</t>
@@ -59,6 +62,9 @@
   </si>
   <si>
     <t>每日任务</t>
+  </si>
+  <si>
+    <t>#</t>
   </si>
   <si>
     <t>福利任务</t>
@@ -1026,121 +1032,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:D20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="3"/>
+  <dimension ref="A3:E20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="12.25" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="1"/>
+    <col min="4" max="5" width="12.25" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:4">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:5">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:4">
+      <c r="E3" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:5">
       <c r="C4" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:4">
+      <c r="E4" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:5">
       <c r="C5" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:4">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:5">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:4">
+        <v>6</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:5">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" s="3" customFormat="1" customHeight="1" spans="3:4">
+        <v>7</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="3" customFormat="1" customHeight="1" spans="3:5">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" s="3" customFormat="1" customHeight="1" spans="3:4">
+        <v>8</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" s="3" customFormat="1" customHeight="1" spans="3:5">
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-    </row>
-    <row r="10" s="3" customFormat="1" customHeight="1" spans="3:4">
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" s="3" customFormat="1" customHeight="1" spans="3:5">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-    </row>
-    <row r="11" s="3" customFormat="1" customHeight="1" spans="3:4">
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" s="3" customFormat="1" customHeight="1" spans="3:5">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-    </row>
-    <row r="12" s="3" customFormat="1" customHeight="1" spans="3:4">
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" s="3" customFormat="1" customHeight="1" spans="3:5">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
-    </row>
-    <row r="13" s="3" customFormat="1" customHeight="1" spans="3:4">
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" s="3" customFormat="1" customHeight="1" spans="3:5">
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
-    </row>
-    <row r="14" s="3" customFormat="1" customHeight="1" spans="3:4">
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" s="3" customFormat="1" customHeight="1" spans="3:5">
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
-    </row>
-    <row r="15" s="3" customFormat="1" customHeight="1" spans="3:4">
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" s="3" customFormat="1" customHeight="1" spans="3:5">
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-    </row>
-    <row r="16" s="3" customFormat="1" customHeight="1" spans="3:4">
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" s="3" customFormat="1" customHeight="1" spans="3:5">
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
-    </row>
-    <row r="17" s="3" customFormat="1" customHeight="1" spans="3:4">
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" s="3" customFormat="1" customHeight="1" spans="1:5">
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
-    </row>
-    <row r="18" s="3" customFormat="1" customHeight="1" spans="3:4">
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" s="3" customFormat="1" customHeight="1" spans="1:5">
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
-    </row>
-    <row r="19" s="3" customFormat="1" customHeight="1" spans="3:4">
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" s="3" customFormat="1" customHeight="1" spans="1:5">
       <c r="C19" s="1">
         <v>11</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" s="3" customFormat="1" customHeight="1" spans="3:4">
+        <v>9</v>
+      </c>
+      <c r="E19" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" s="3" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C20" s="1">
         <v>12</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="E20" s="3">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/AchievementTaskGroupConfig.xlsx
+++ b/Excel/AchievementTaskGroupConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
   <si>
     <t>_id</t>
   </si>
@@ -62,9 +62,6 @@
   </si>
   <si>
     <t>每日任务</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
   <si>
     <t>福利任务</t>
@@ -1032,7 +1029,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:E20"/>
+  <dimension ref="C3:E20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1146,17 +1143,17 @@
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" s="3" customFormat="1" customHeight="1" spans="1:5">
+    <row r="17" s="3" customFormat="1" customHeight="1" spans="3:5">
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" s="3" customFormat="1" customHeight="1" spans="1:5">
+    <row r="18" s="3" customFormat="1" customHeight="1" spans="3:5">
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" s="3" customFormat="1" customHeight="1" spans="1:5">
+    <row r="19" s="3" customFormat="1" customHeight="1" spans="3:5">
       <c r="C19" s="1">
         <v>11</v>
       </c>
@@ -1167,18 +1164,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" s="3" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>10</v>
-      </c>
+    <row r="20" s="3" customFormat="1" customHeight="1" spans="3:5">
       <c r="C20" s="1">
         <v>12</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E20" s="3">
         <v>30</v>

--- a/Excel/AchievementTaskGroupConfig.xlsx
+++ b/Excel/AchievementTaskGroupConfig.xlsx
@@ -1161,7 +1161,7 @@
         <v>9</v>
       </c>
       <c r="E19" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" customHeight="1" spans="3:5">
@@ -1172,7 +1172,7 @@
         <v>10</v>
       </c>
       <c r="E20" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
